--- a/data_extactor/batch_10_fa/batch_0053_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0053_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Allscripts healthcare automation software | Boston Bar Systems Corporation Sonnet | Bytescribe Development Company WavPlayer | نرم‌افزار تقویم | Corel WordPerfect Office Suite | Crescendo Systems Corporation MedRite-XL | Crescendo Systems DigiScribe-XL | نرم‌افزار پایگاه داده | سیستم‌های پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Emmaus MPWord | FileMaker Pro | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | Integrated Systems Management OmniMD | MedQuist DocQment Enterprise Platform | پایگاه‌های داده اصطلاحات پزشکی | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Narratek Smartype | Nuance Dragon NaturallySpeaking | PCC EHR | نرم‌افزار صورتحساب بیمار | Precision Data Solutions VoicePower | Prognosis Innovation Healthcare ChartAccess | SpectraMedi EasyFlow | نرم‌افزار تشخیص گفتار | SpeedType | SpeedUp Trans | Spellex AccuCount | Sylvan Software Complete Medical Pharmaceutical Spell Checker | Sylvan Software DropChute Pro | Sylvan Software ShortCut | نرم‌افزار مرورگر وب | YouTube | dBASE Plus | نرم‌افزار eClinicalWorks EHR | g-net solutions MTP</t>
+          <t>نرم‌افزار اتوماسیون مراقبت‌های بهداشتی Allscripts | Boston Bar Systems Corporation Sonnet | Bytescribe Development Company WavPlayer | نرم‌افزار تقویم | Corel WordPerfect Office Suite | Crescendo Systems Corporation MedRite-XL | Crescendo Systems DigiScribe-XL | نرم‌افزار پایگاه داده | سیستم‌های پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Emmaus MPWord | FileMaker Pro | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Integrated Systems Management OmniMD | MedQuist DocQment Enterprise Platform | پایگاه‌های داده اصطلاحات پزشکی | Microsoft ASP.NET | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Narratek Smartype | Nuance Dragon NaturallySpeaking | PCC EHR | نرم‌افزار صورتحساب بیمار | Precision Data Solutions VoicePower | Prognosis Innovation Healthcare ChartAccess | SpectraMedi EasyFlow | نرم‌افزار تشخیص گفتار | SpeedType | SpeedUp Trans | Spellex AccuCount | Sylvan Software Complete Medical Pharmaceutical Spell Checker | Sylvan Software DropChute Pro | Sylvan Software ShortCut | نرم‌افزار مرورگر وب | YouTube | dBASE Plus | نرم‌افزار eClinicalWorks EHR | g-net solutions MTP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | نگارش | مانیتورینگ | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اداری | کامپیوتر و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | بیان شفاهی | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | چالاکی انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | مهارت انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه یا تیم کاری | اهمیت تکرار وظایف مشابه | ایمیل | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان به صورت نشسته | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | ایمیل | ارتباط با دیگران | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان قلب | تکنسین‌ها و تکنولوژیست‌های قلبی عروقی | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | بایگان‌ها | تکنولوژیست‌های اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | تکنولوژیست‌های نورودیاگنوستیک | جراحان ارتوپد، به جز اطفال | پیراپزشکان | جراحان اطفال | تکنسین‌های داروخانه | فلبوتومیست‌ها | تکنسین‌ها و تکنولوژیست‌های رادیولوژی | پذیرش‌کنندگان و متصدیان اطلاعات | پردازشگران واژه و تایپیست‌ها</t>
+          <t>متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کارمندان بایگانی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | دستیاران پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | تکنولوژیست‌های نورودیاگنوستیک | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | تکنسین‌های داروسازی | فلبوتومیست‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | متصدیان پذیرش و کارمندان اطلاعات | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | درک کتبی | حساسیت به مسئله | سازماندهی اطلاعات | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی</t>
+          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | صرف زمان به صورت ایستاده | ارتباط با دیگران | کار با یا مشارکت در یک گروه یا تیم کاری | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف مشابه | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان برای ایستادن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | ایمیل | آزادی در تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوقداران | متصدیان پیشخوان و اجاره | نمایندگان خدمات مشتریان | سرپرستان خط اول کارکنان فروش خرده‌فروشی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | آماده‌کنندگان تجهیزات پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | دستیاران پرستار | کارمندان دفتری، عمومی | عینک‌سازان، توزیع‌کننده | داروسازان | تکنسین‌های داروخانه | فلبوتومیست‌ها | پذیرش‌کنندگان و متصدیان اطلاعات | فروشندگان خرده‌فروشی | چیدمان‌کنندگان و پرکنندگان سفارش | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
+          <t>صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | سرپرستان رده اول کارکنان فروش خرده‌فروشی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | کمک‌پرستاران | کارمندان دفتری عمومی | عینک‌سازان، توزیع‌کننده | داروسازان | تکنسین‌های داروسازی | فلبوتومیست‌ها | متصدیان پذیرش و کارمندان اطلاعات | فروشندگان خرده‌فروشی | قفسه‌چین‌ها و پرکننده‌های سفارش | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories IDEXX Cornerstone | نرم‌افزار برچسب‌گذاری | McAllister Software Systems AVImark | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مدیریت مطب PMS | نرم‌افزار برنامه‌ریزی</t>
+          <t>IDEXX Laboratories IDEXX Cornerstone | نرم‌افزار برچسب‌زنی Labeling software | McAllister Software Systems AVImark | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مدیریت مطب PMS | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | مانیتورینگ | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | زیست‌شناسی | اداری | پزشکی و دندانپزشکی | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | سازماندهی اطلاعات | چالاکی دست | استدلال قیاسی | بینایی نزدیک | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری گسترده | قدرت تنه | هماهنگی چند عضو | چالاکی انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت دستی | استدلال قیاسی | بینایی نزدیک | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت ایستاده | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | در معرض آلاینده‌ها | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | در معرض تابش | پیامد خطا | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفسی، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تابش | ایمیل | در معرض فضای کاری تنگ، موقعیت‌های نامناسب | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای ایستادن | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فشار زمانی | قرار گرفتن در معرض تابش | پیامد خطا | تعامل با مشتریان خارجی یا عموم مردم | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | ایمیل | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آلرژیست‌ها و ایمونولوژیست‌ها | مراقبان حیوانات | تکنسین‌ها و تکنولوژیست‌های قلبی عروقی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | دستیاران سلامت در خانه | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | تکنولوژیست‌های آزمایشگاهی پزشکی و بالینی | پرستاران متخصص | دستیاران پرستار | پیراپزشکان | داروسازان | فلبوتومیست‌ها | دستیاران پزشک | پزشکان، آسیب‌شناسان | پرستاران ثبت‌نام شده | دستیاران جراحی | دامپزشکان | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | مراقبان حیوانات | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | پرستاران متخصص | کمک‌پرستاران | پارامدیک‌ها | داروسازان | فلبوتومیست‌ها | دستیاران پزشک | پزشکان، آسیب‌شناسان | پرستاران ثبت‌شده | دستیاران جراحی | دامپزشکان | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Donor management system software | نرم‌افزار پرونده الکترونیک سلامت EMR | Iatric Systems MobiLab | JavaScript | سیستم اطلاعات آزمایشگاهی LIS | MEDITECH Blood Bank | MEDITECH Laboratory and Microbiology | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری پروسیجرهای پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار برنامه‌ریزی</t>
+          <t>Donor management system software | نرم‌افزار پرونده الکترونیک سلامت EMR | Iatric Systems MobiLab | JavaScript | سیستم اطلاعات آزمایشگاهی LIS | MEDITECH Blood Bank | MEDITECH Laboratory and Microbiology | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | مانیتورینگ | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | اداری | آموزش و پرورش | روانشناسی | کامپیوتر و الکترونیک | پزشکی و دندانپزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | چالاکی انگشتان | تشخیص گفتار | سازماندهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | چالاکی دست | توجه انتخابی | سرعت ادراکی</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | مهارت انگشتان | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | مهارت دستی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه یا تیم کاری | در معرض بیماری‌ها یا عفونت‌ها | پیامد خطا | فشار زمانی | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان به صورت ایستاده | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف مشابه | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | داخل ساختمان، محیط کنترل‌شده | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای راه رفتن یا دویدن | موقعیت‌های درگیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامد خطا | فشار زمانی | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | محیط داخلی، دارای کنترل شرایط محیطی | نزدیکی فیزیکی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای راه رفتن یا دویدن | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و تکنولوژیست‌های قلبی عروقی | سیتوتکنولوژیست‌ها | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنسین‌های بافت‌شناسی | هیستوتکنولوژیست‌ها | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشکی | متخصصان مدارک پزشکی | تکنسین‌های آزمایشگاهی پزشکی و بالینی | تکنولوژیست‌های آزمایشگاهی پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | بیهوش‌دهندگان پرستار | دستیاران پرستار | پیراپزشکان | تکنسین‌ها و تکنولوژیست‌های رادیولوژی | دستیاران جراحی | تکنسین‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
+          <t>تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سیتوتکنولوژیست‌ها | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | متخصصان مدارک پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | پرستاران بیهوشی | کمک‌پرستاران | پارامدیک‌ها | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری پروسیجرهای پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | نرم‌افزار مرورگر وب | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | زبان انگلیسی | روانشناسی | کامپیوتر و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | سازماندهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها | قدرت ایستا | قدرت تنه | استقامت</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | قدرت ایستا | قدرت تنه | استقامت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه یا تیم کاری | فشار زمانی | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم شدن یا پیچاندن بدن | اهمیت تکرار وظایف مشابه | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای خم کردن یا چرخاندن بدن | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دستیاران پرستار | خدمه بیمارستان | دستیاران سلامت در خانه | دستیاران مراقبت شخصی | دستیاران روانپزشکی | دستیاران پزشکی | دستیاران دندانپزشکی | دستیاران فیزیوتراپی | دستیاران کاردرمانی | دستیاران داروخانه | آماده‌کنندگان تجهیزات پزشکی | فلبوتومیست‌ها | تکنسین‌های آندوسکوپی | دستیاران آسیب‌شناسی گفتار-زبان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | پرستاران عملی و حرفه‌ای دارای مجوز | پرستاران ثبت‌نام شده | تکنولوژیست‌ها و تکنسین‌های بهداشتی، سایر | متخصصان مدارک پزشکی | نمایندگان بیمار</t>
+          <t>کمک‌پرستاران | بهیاران | کمک‌یاران سلامت در منزل | کمک‌یاران مراقبت شخصی | کمک‌یاران روان‌پزشکی | دستیاران پزشکی | دستیاران دندان‌پزشکی | کمک‌یاران فیزیوتراپی | کمک‌یاران کاردرمانی | دستیاران داروخانه | آماده‌سازان تجهیزات پزشکی | فلبوتومیست‌ها | تکنسین‌های آندوسکوپی | دستیاران آسیب‌شناسی گفتار-زبان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | پرستاران ثبت‌شده | تکنولوژیست‌ها و تکنسین‌های سلامت، همه مشاغل دیگر | متخصصان مدارک پزشکی | نمایندگان بیمار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Adobe Audition | نرم‌افزار بیوفیدبک | Bungalow Software Aphasia Tutor | ELR Software eLr Extra Language Resources | نرم‌افزار ایمیل | KayPENTAX Multi-Speech | نرم‌افزار تحلیل زبان | Learning Fundamentals Speech Visualization | Micro Video Video Voice Speech Training System | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Propeller Multimedia React2 | نرم‌افزار تحلیل سیگنال | نرم‌افزار تحلیل گفتار | نرم‌افزار متن به گفتار | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Audition | نرم‌افزار بیوفیدبک | Bungalow Software Aphasia Tutor | ELR Software eLr Extra Language Resources | نرم‌افزار ایمیل | KayPENTAX Multi-Speech | نرم‌افزار تحلیل زبان | Learning Fundamentals Speech Visualization | Micro Video Video Voice Speech Training System | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | Propeller Multimedia React2 | نرم‌افزار تحلیل سیگنال | نرم‌افزار تحلیل گفتار | نرم‌افزار تبدیل متن به گفتار | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | مانیتورینگ | تفکر انتقادی | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | روانشناسی | خدمات مشتریان و شخصی | اداری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | سازماندهی اطلاعات | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت شنوایی | اصالت | روان بودن ایده‌ها | اشتراک زمانی | توجه شنوایی</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت شنوایی | اصالت | روانی ایده‌ها | تقسیم توجه | توجه شنیداری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه یا تیم کاری | مکالمات تلفنی | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان به صورت نشسته | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ایمیل | نزدیکی فیزیکی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران پیشرفته روانپزشکی | شنوایی‌شناسان | متخصصان قلب | تکنسین‌ها و تکنولوژیست‌های قلبی عروقی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | متخصصان سمعک | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | دستیاران پزشکی | کاردرمانگران | دستیاران کاردرمانی | دستیاران کاردرمانی | جراحان اطفال | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | دستیاران روانپزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مشاوران توانبخشی | آسیب‌شناسان گفتار-زبان</t>
+          <t>پرستاران پیشرفته روانپزشکی | شنوایی‌شناسان | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پرستاری بالینی | پزشکان طب اورژانس | متخصصان سمعک | درمانگران کم‌بینایی، متخصصان جهت‌یابی و تحرک، و درمانگران توانبخشی بینایی | دستیاران پزشکی | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | جراحان کودکان | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | کمک‌یاران روان‌پزشکی | تکنسین‌های روانپزشکی | درمانگران تفریحی | مشاوران توانبخشی | آسیب‌شناسان گفتار و زبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار ایمیل | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار برنامه‌ریزی</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | مانیتورینگ</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی | پزشکی و دندانپزشکی | آموزش و پرورش | کامپیوتر و الکترونیک | تولید و فرآوری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | رایانه و الکترونیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | چالاکی انگشتان | استدلال قیاسی | سازماندهی اطلاعات | چالاکی دست | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | هماهنگی چند عضو</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | مهارت انگشتان | استدلال قیاسی | ترتیب‌دهی اطلاعات | مهارت دستی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، محیط کنترل‌شده | ارتباط با دیگران | صرف زمان به صورت ایستاده | در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه یا تیم کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | در معرض آلاینده‌ها | اهمیت تکرار وظایف مشابه | پیامد خطا | صرف زمان برای انجام حرکات تکراری | ایمیل | فشار زمانی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای ایستادن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | اهمیت تکرار وظایف یکسان | پیامد خطا | صرف زمان برای انجام حرکات تکراری | ایمیل | فشار زمانی | مکالمات تلفنی | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران پزشک بیهوشی | متخصصان قلب | تکنسین‌ها و تکنولوژیست‌های قلبی عروقی | سونوگرافیست‌های تشخیص پزشکی | دستیاران پزشکی | آماده‌کنندگان تجهیزات پزشکی | تکنسین‌های آزمایشگاهی پزشکی و بالینی | تکنولوژیست‌های آزمایشگاهی پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | درمانگران پرتو | تکنسین‌ها و تکنولوژیست‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | قانون و حکومت | مدیریت و سازماندهی | روانشناسی | زبان انگلیسی | اداری | کامپیوتر و الکترونیک | آموزش و پرورش | پرسنل و منابع انسانی | خدمات مشتریان و شخصی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | روان‌شناسی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | سازماندهی اطلاعات | توجه شنوایی | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | قدرت تنه | قدرت انفجاری | استقامت | جهت‌گیری پاسخ | اشتراک زمانی | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | تعادل کلی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | ترتیب‌دهی اطلاعات | توجه شنیداری | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | قدرت تنه | قدرت انفجاری | استقامت | جهت‌گیری پاسخ | تقسیم توجه | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه یا تیم کاری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های درگیری | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | فشار زمانی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | در معرض بیماری‌ها یا عفونت‌ها | اهمیت تکرار وظایف مشابه | خارج از ساختمان، در معرض همه شرایط آب و هوایی | صرف زمان برای راه رفتن یا دویدن</t>
+          <t>ایمیل | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | فشار زمانی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سخنرانی عمومی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت تکرار وظایف یکسان | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | ضابطان دادگستری | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | سرپرستان خط اول کارکنان تفریحی و سرگرمی، به جز خدمات قمار | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان خط اول کارکنان پشتیبانی دفتری و اداری | سرپرستان خط اول مهمانداران مسافر | سرپرستان خط اول کارکنان خدمات شخصی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | مدیران خدمات پزشکی و بهداشتی | افسران گشت پلیس و کلانتر | افسران تعلیقی و متخصصان درمان اصلاحی | مشاوران توانبخشی | مشاوران اقامتی | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | پلیس ترانزیت و راه‌آهن</t>
+          <t>مدیران خدمات اداری | ضابطان دادگستری | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | مدیران خدمات پزشکی و بهداشتی | ماموران گشت پلیس و کلانتر | افسران مشروط و متخصصان درمان اصلاحی | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | مدیران خدمات اجتماعی و جامعه | دستیاران خدمات اجتماعی و انسانی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار ترسیم چهره نگاری رایانه‌ای | نرم‌افزار اعزام به کمک کامپیوتر | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | DesignWare 3D EyeWitness | نرم‌افزار ایمیل | سیستم یکپارچه شناسایی خودکار اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | نرم‌افزار برنامه‌ریزی | SmartDraw Legal | Spillman Technologies Records Management | The CAD Zone The Crime Zone</t>
+          <t>نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | نرم‌افزار اعزام به کمک کامپیوتر | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | DesignWare 3D EyeWitness | نرم‌افزار ایمیل | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visio | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | نرم‌افزار زمان‌بندی | SmartDraw Legal | Spillman Technologies Records Management | The CAD Zone The Crime Zone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | قانون و حکومت | خدمات مشتریان و شخصی | مدیریت و سازماندهی | زبان انگلیسی | روانشناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | آموزش و پرورش | پرسنل و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | روان بودن ایده‌ها | بینایی دور | چالاکی دست | ثبات دست و بازو | سرعت ادراکی | سرعت بستار | حفظ کردن | اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | روانی ایده‌ها | بینایی دور | مهارت دستی | ثبات دست و بازو | سرعت ادراکی | سرعت بستار | حفظ کردن | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه یا تیم کاری | خارج از ساختمان، در معرض همه شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | موقعیت‌های درگیری | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، محیط کنترل‌شده | پیامد خطا | در معرض تجهیزات خطرناک | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | در معرض بیماری‌ها یا عفونت‌ها | در معرض دماهای بسیار گرم یا سرد | فشار زمانی</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | موقعیت‌های تعارض | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ضابطان دادگستری | مدیران ارشد اجرایی | افسران انطباق | پزشکان قانونی | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان پشتیبانی دفتری و اداری | سرپرستان خط اول مهمانداران مسافر | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیاتی | تحلیلگران اطلاعاتی | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران تعلیقی و متخصصان درمان اصلاحی | اپراتورهای مخابراتی امنیت عمومی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
+          <t>ضابطان دادگستری | مدیران ارشد اجرایی | افسران انطباق | بازرسان مرگ | افسران اصلاح و تربیت و زندانبانان | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارکنان امنیتی | مدیران عمومی و عملیات | تحلیلگران اطلاعاتی | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | اپراتورهای مخابراتی امنیت عمومی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | مانیتورینگ | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | خدمات مشتریان و شخصی | آموزش و پرورش | ساختمان و ساخت و ساز | مدیریت و سازماندهی | زبان انگلیسی | مکانیک | قانون و حکومت | پرسنل و منابع انسانی | اداری | پزشکی و دندانپزشکی | روانشناسی | شیمی | حمل و نقل | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | ساختمان و ساخت‌وساز | مدیریت و اداره | زبان انگلیسی | مکانیک | قانون و دولت | پرسنل و منابع انسانی | اداری | پزشکی و دندان‌پزشکی | روان‌شناسی | شیمی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | سازماندهی اطلاعات | تشخیص گفتار | وضوح گفتار | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | سرعت ادراکی | توجه انتخابی | چالاکی دست | قدرت تنه | بینایی دور | قدرت انفجاری | قدرت ایستا | ثبات دست و بازو | تجسم فضایی | چالاکی انگشتان | اشتراک زمانی | انعطاف‌پذیری بستار | سرعت بستار | تعادل کلی بدن | انعطاف‌پذیری گسترده | هماهنگی چند عضو | دقت کنترل | تشخیص رنگ‌های بصری</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | سرعت ادراکی | توجه انتخابی | مهارت دستی | قدرت تنه | بینایی دور | قدرت انفجاری | قدرت ایستا | ثبات دست و بازو | تجسم | مهارت انگشتان | تقسیم توجه | انعطاف‌پذیری بستار | سرعت بستار | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه یا تیم کاری | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | ایمیل | خارج از ساختمان، در معرض همه شرایط آب و هوایی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | در معرض دماهای بسیار گرم یا سرد | داخل ساختمان، محیط غیرکنترل‌شده | در معرض آلاینده‌ها | در معرض تجهیزات خطرناک | استفاده از تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفسی، مهار ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تابش | داخل ساختمان، محیط کنترل‌شده | در معرض شرایط خطرناک | در معرض بیماری‌ها یا عفونت‌ها | در معرض شرایط نوری بسیار روشن یا ناکافی | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سطح رقابت</t>
+          <t>سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | ایمیل | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | آزادی در تصمیم‌گیری | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نزدیکی فیزیکی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سطح رقابت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان عملیات فرودگاه | بازرسان ساخت و ساز و ساختمان | مدیران مدیریت بحران | بازرسان و کارآگاهان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش | آتش‌نشانان | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارکنان تفریحی و سرگرمی، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگلداری | سرپرستان خط اول اپراتورهای ماشین‌آلات جابجایی مواد و وسایل نقلیه | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول مهمانداران مسافر | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | بازرسان آتش‌سوزی جنگل و متخصصان پیشگیری | مهندسان ایمنی و بهداشت، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | افسران گشت پلیس و کلانتر | مهندسان کشتی</t>
+          <t>متخصصان عملیات فرودگاه | بازرسان ساختمان و ساخت‌وساز | مدیران مدیریت بحران | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | آتش‌نشانان | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | ماموران گشت پلیس و کلانتر | مهندسان کشتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0053_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0053_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | نظارت | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | نظارت | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | دید نزدیک | بیان شفاهی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | وضوح گفتار | چابکی انگشتان | سرعت ادراک | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | تشخیص گفتار | بیان کتبی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | وضوح گفتار | مهارت انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | تکنسین‌ها و کارشناسان فناوری قلب و عروق | تندنویسان و ثبت‌کنندگان هم‌زمان جلسات دادگاه | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | بایگان‌ها و کارمندان امور اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | دستیاران پزشک | کارشناسان مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌های پزشکی و مسئولان دفاتر درمانی | کارشناسان فناوری الکترودیاگنوز عصبی | جراحان ارتوپدی (غیر از اطفال) | کارشناسان فوریت‌های پزشکی (پارامدیک) | جراحان اطفال | تکنسین‌های دارویی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و فناوری‌های پرتوشناختی | متصدیان پذیرش و کارمندان اطلاعات | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | متصدیان بایگانی و اسناد | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کمک‌پزشکان و دستیاران مطب | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | تکنسین‌های الکترونورودیاگنوستیک | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کارشناسان و تکنسین‌های خون‌گیری | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متصدیان پذیرش و اطلاعات | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | دید نزدیک | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی انگشتان | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | بیان کتبی</t>
+          <t>درک شفاهی | وضوح گفتار | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوق‌داران | متصدیان باجه و کرایه کالا | کارشناسان پاسخگویی و خدمات مشتریان | سرپرستان رده‌اول فروشگاه‌ها و خرده‌فروشی‌ها | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | تکنسین‌های آماده‌سازی و استریلیزاسیون تجهیزات پزشکی | کارشناسان مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌های پزشکی و مسئولان دفاتر درمانی | کمک‌بهیاران | کارمندان امور اداری و دفتری | عینک‌سازان (ساخت و فروش عینک) | داروسازان | تکنسین‌های دارویی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | متصدیان پذیرش و کارمندان اطلاعات | فروشندگان خرده‌فروشی | انبارداران و متصدیان جمع‌آوری و چیدمان کالا | دستیاران دامپزشکی و نگهداران حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
+          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان خرده‌فروشی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | کمک‌پرستاران | متصدیان امور دفتری و امور عمومی اداری | عینک‌سازان (ساخت و فروش عینک) | داروسازان | تکنسین‌های داروخانه (نسخه‌پیچ‌ها) | کارشناسان و تکنسین‌های خون‌گیری | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | متصدیان چیدمان و آماده‌سازی سفارش | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | زیست‌شناسی | امور اداری و دفتری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | زیست‌شناسی | اداری | پزشکی و دندان‌پزشکی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی دستی | استدلال قیاسی | دید نزدیک | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌مفصلی | قدرت تنه | هماهنگی چندعضوی | چابکی انگشتان | پایداری دست و بازو | توجه انتخابی | انعطاف‌پذیری در بستن الگوها | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت دستی | استدلال قیاسی | بینایی نزدیک | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | توجه انتخابی | انعطاف‌پذیری بستار | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی بالینی | مراقبان و نگهداران حیوانات | تکنسین‌ها و کارشناسان فناوری قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | کارشناسان و تکنسین‌های آزمایشگاه‌های بالینی و پاتولوژی | پرستاران دوره‌دیده مراقبت‌های بالینی پیشرفته | کمک‌بهیاران | کارشناسان فوریت‌های پزشکی (پارامدیک) | داروسازان | کارشناسان خون‌گیری (فلبوتومیست‌ها) | دستیاران بالینی پزشک | پزشکان متخصص پاتولوژی (آسیب‌شناسی) | پرستاران دارای پروانه کار (RN) | دستیاران اتاق عمل و جراحی | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | مراقبان و نگهداران حیوانات | کارشناسان و تکنسین‌های قلب و عروق | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | کارشناسان علوم آزمایشگاهی بالینی | پرستاران بالینی پیشرفته | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | داروسازان | کارشناسان و تکنسین‌های خون‌گیری | دستیاران پزشک | پزشکان متخصص پاتولوژی | پرستاران | دستیاران جراحی | دامپزشکان | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | پایداری دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | چابکی انگشتان | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستن الگوها | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان کتبی | چابکی دستی | توجه انتخابی | سرعت ادراک</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | مهارت انگشتان | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | مهارت دستی | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری قلب و عروق | تکنسین‌های سایتولوژی (سلول‌شناسی) | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | تکنسین‌های بافت‌شناسی (هیستولوژی) | متخصصان و کارشناسان بافت‌شناسی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشک | کارشناسان مدارک پزشکی و فناوری اطلاعات سلامت | تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان و تکنسین‌های آزمایشگاه‌های بالینی و پاتولوژی | کارشناسان فناوری الکترودیاگنوز عصبی | کارشناسان بیهوشی (هوشبری) | کمک‌بهیاران | کارشناسان فوریت‌های پزشکی (پارامدیک) | تکنسین‌ها و کارشناسان رادیولوژی و فناوری‌های پرتوشناختی | دستیاران اتاق عمل و جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
+          <t>کارشناسان و تکنسین‌های قلب و عروق | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | پرستاران بیهوشی | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | دستیاران جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | توانایی به‌خاطرسپاری | روانی ایده‌ها | قدرت ایستا | قدرت تنه | استقامت بدنی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | قدرت ایستا | قدرت تنه | استقامت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کمک‌بهیاران | خدمات‌دهندگان و برانکاردبران مراکز درمانی | مراقبان سلامت در منزل | مراقبان خدمات شخصی | نیروهای کمکی بخش روان‌پزشکی | دستیاران پزشک | دستیاران دندان‌پزشک | دستیاران فیزیوتراپی | دستیاران کاردرمانی | کمک‌متصدیان داروخانه | تکنسین‌های آماده‌سازی و استریلیزاسیون تجهیزات پزشکی | کارشناسان خون‌گیری (فلبوتومیست‌ها) | تکنسین‌های اندوسکوپی | دستیاران گفتاردرمانی | دستیاران دامپزشکی و نگهداران حیوانات آزمایشگاهی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران دارای پروانه کار (RN) | سایر متخصصان و تکنسین‌های حوزه سلامت | کارشناسان مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان امور پیگیری و حقوق بیماران</t>
+          <t>کمک‌پرستاران | خدمات‌دهندگان و انتقال‌دهندگان بیمار | مراقبان سلامت و بهیاران مراقبت در منزل | مراقبان خدمات شخصی و همراهان توان‌خواهان | کمک‌یاران بخش روان‌پزشکی | کمک‌پزشکان و دستیاران مطب | دستیاران دندان‌پزشک | کمک‌یاران فیزیوتراپی | کمک‌یاران کاردرمانی | کمک‌متصدیان داروخانه | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان و تکنسین‌های خون‌گیری | تکنسین‌های اندوسکوپی | دستیاران آسیب‌شناسی گفتار و زبان (گفتاردرمانی) | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | بهیاران و کمک‌پرستاران دارای مجوز | پرستاران | سایر متخصصان و تکنسین‌های حوزه سلامت | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | کارشناسان امور بیماران و پذیرش</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | آموزش و تدریس | درمان و مشاوره‌های توانبخشی | روان‌شناسی | خدمات مشتریان و خدمات فردی | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | آموزش و پرورش | درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت شنوایی | ابتکار و اصالت | روانی ایده‌ها | تقسیم توجه | توجه شنیداری</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال استقرایی | استدلال قیاسی | حساسیت شنوایی | اصالت | روانی ایده‌ها | تقسیم توجه | توجه شنیداری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران دوره‌دیده روان‌پزشکی بالینی | شنوایی‌شناسان (ادیولوژیست‌ها) | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان فناوری قلب و عروق | کارشناسان ارشد بالینی پرستاری | پزشکان طب اورژانس | متخصصان تجویز سمعک و ارزیابی شنوایی | کارشناسان توانبخشی کم‌بینایی، جهت‌یابی و حرکت | دستیاران پزشک | کاردرمانگران | دستیاران کاردرمانی | تکنسین‌ها و کاردان‌های کاردرمانی | جراحان اطفال | دستیاران فیزیوتراپی | تکنسین‌ها و کاردان‌های فیزیوتراپی | نیروهای کمکی بخش روان‌پزشکی | تکنسین‌های خدمات سلامت روان و روان‌پزشکی | کارشناسان تفریح‌درمانی | مشاوران توانبخشی شغلی و ناتوانی‌ها | کارشناسان و آسیب‌شناسان گفتار و زبان (گفتاردرمانگران)</t>
+          <t>پرستاران تخصصی روانپزشکی | شنوایی‌شناسان | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پزشکان طب اورژانس | کارشناسان تجویز و ساخت سمعک | متخصصان جهت‌یابی، حرکت و توانبخشی نابینایان و کم‌بینایان | کمک‌پزشکان و دستیاران مطب | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | جراحان اطفال | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | کمک‌یاران بخش روان‌پزشکی | تکنسین‌های روان‌پزشکی و بهداشت روان | کارشناسان تفریح‌درمانی | مشاوران توانبخشی | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | نگارش | سخن گفتن | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | آموزش و تدریس | رایانه و الکترونیک | تولید و فرآوری</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | رایانه و الکترونیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | پایداری دست و بازو | چابکی انگشتان | استدلال قیاسی | مرتب‌سازی اطلاعات | چابکی دستی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | دقت کنترل | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | استدلال استقرایی | هماهنگی چندعضوی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | بیان شفاهی | درک کتبی | ثبات دست و بازو | مهارت انگشتان | استدلال قیاسی | ترتیب‌دهی اطلاعات | مهارت دستی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | بیان کتبی | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>پرستاران بخش‌های ویژه و مراقبت حاد | دستیاران متخصص بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان فناوری قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | دستیاران پزشک | تکنسین‌های آماده‌سازی و استریلیزاسیون تجهیزات پزشکی | تکنسین‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان و تکنسین‌های آزمایشگاه‌های بالینی و پاتولوژی | کارشناسان فناوری الکترودیاگنوز عصبی | تکنسین‌های معاینات چشم‌پزشکی | کارشناسان فناوری‌های اپتومتری و چشم‌پزشکی | جراحان ارتوپدی (غیر از اطفال) | جراحان اطفال | کارشناسان پرتوپزشکی و پرتودرمانی | تکنسین‌ها و کارشناسان رادیولوژی و فناوری‌های پرتوشناختی | پزشکان متخصص رادیولوژی | کارشناسان درمان‌های تنفسی | دستیاران اتاق عمل و جراحی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مدیریت و امور اداری | روان‌شناسی | زبان انگلیسی | امور اداری و دفتری | رایانه و الکترونیک | آموزش و تدریس | امور پرسنلی و منابع انسانی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره‌های توانبخشی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | روان‌شناسی | زبان انگلیسی | اداری | رایانه و الکترونیک | آموزش و پرورش | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | دید نزدیک | دید دور | مرتب‌سازی اطلاعات | توجه شنیداری | قدرت ایستا | زمان واکنش | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | قدرت تنه | قدرت انفجاری | استقامت بدنی | جهت‌یابی پاسخ | تقسیم توجه | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | تعادل عمومی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | بینایی دور | ترتیب‌دهی اطلاعات | توجه شنیداری | قدرت ایستا | زمان عکس‌العمل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | قدرت تنه | قدرت انفجاری | استقامت | جهت‌گیری پاسخ | تقسیم توجه | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تعادل کلی بدن</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری و پشتیبانی | دادرسان و ضابطان امور قضایی | ماموران مراقبت و زندان‌بانان | کارآگاهان و بازرسان کشف جرایم | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی (به‌جز مراکز شرط‌بندی) | سرپرستان رده‌اول کارکنان خدمات و نظافت اماکن | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول کارکنان امور اداری و دفتری | سرپرستان رده‌اول مهمانداران و مهمانداران خدمات مسافری | سرپرستان رده‌اول ارائه‌دهندگان خدمات فردی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول نگهبانان و ماموران حراست | مدیران خدمات بهداشتی و درمانی | ماموران گشت پلیس و کلانتری | افسران مراقبت‌های پس از خروج و مددکاران بازپروری زندانیان | مشاوران توانبخشی شغلی و ناتوانی‌ها | مشاوران امور اقامتگاه‌ها و خوابگاه‌ها | مدیران خدمات اجتماعی و امور عام‌المنفعه | دستیاران خدمات اجتماعی و مددکاری | پلیس خطوط ریلی و سامانه‌های ترانزیت</t>
+          <t>مدیران خدمات اداری و پشتیبانی | مأموران انتظامات و حفاظت دادگاه | مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران خدمات درمانی و بهداشتی | ماموران گشت پلیس و کلانتری | مددکاران قضایی و متخصصان اصلاح و تربیت | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | مدیران خدمات اجتماعی و خدمات مردمی | دستیاران خدمات اجتماعی و انسانی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره‌های توانبخشی | آموزش و تدریس | امور پرسنلی و منابع انسانی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره | آموزش و پرورش | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | دید نزدیک | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در بستن الگوها | روانی ایده‌ها | دید دور | چابکی دستی | پایداری دست و بازو | سرعت ادراک | سرعت بستن الگوها | توانایی به‌خاطرسپاری | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | روانی ایده‌ها | بینایی دور | مهارت دستی | ثبات دست و بازو | سرعت ادراکی | سرعت بستار | حفظ کردن | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دادرسان و ضابطان امور قضایی | مدیران ارشد اجرایی | کارشناسان انطباق با قوانین و مقررات | پزشکان قانونی و معاینه‌کنندگان اجساد | ماموران مراقبت و زندان‌بانان | کارآگاهان و بازرسان کشف جرایم | مدیران مدیریت بحران و پدافند غیرعامل | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی | سرپرستان رده‌اول کارکنان امور اداری و دفتری | سرپرستان رده‌اول مهمانداران و مهمانداران خدمات مسافری | سرپرستان رده‌اول نگهبانان و ماموران حراست | مدیران کل و مدیران ارشد عملیاتی | تحلیل‌گران داده‌های اطلاعاتی و امنیتی | ماموران گشت پلیس و کلانتری | کارآگاهان خصوصی و بازرسان غیردولتی | افسران مراقبت‌های پس از خروج و مددکاران بازپروری زندانیان | کارشناسان پیام‌رسانی و فوریت‌های ایمنی عمومی | نگهبانان و ماموران حراست | پلیس خطوط ریلی و سامانه‌های ترانزیت</t>
+          <t>مأموران انتظامات و حفاظت دادگاه | مدیران عامل و مدیران ارشد اجرایی | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | مدیران مدیریت بحران و پدافند غیرعامل | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران کل و مدیران عملیات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | اپراتورهای فوریت‌های پلیسی و امدادی | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ساختمان و سازه | مدیریت و امور اداری | زبان انگلیسی | مکانیک | حقوق و مقررات دولتی | امور پرسنلی و منابع انسانی | امور اداری و دفتری | پزشکی و دندان‌پزشکی | روان‌شناسی | شیمی | ترابری و حمل‌ونقل | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | ساختمان و ساخت‌وساز | مدیریت و اداره | زبان انگلیسی | مکانیک | قانون و دولت | پرسنل و منابع انسانی | اداری | پزشکی و دندان‌پزشکی | روان‌شناسی | شیمی | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | دید نزدیک | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | سرعت ادراک | توجه انتخابی | چابکی دستی | قدرت تنه | دید دور | قدرت انفجاری | قدرت ایستا | پایداری دست و بازو | تجسم فضایی | چابکی انگشتان | تقسیم توجه | انعطاف‌پذیری در بستن الگوها | سرعت بستن الگوها | تعادل عمومی بدن | انعطاف‌مفصلی | هماهنگی چندعضوی | دقت کنترل | تشخیص رنگ‌ها</t>
+          <t>بیان شفاهی | درک شفاهی | حساسیت به مسئله | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | اصالت | سرعت ادراکی | توجه انتخابی | مهارت دستی | قدرت تنه | بینایی دور | قدرت انفجاری | قدرت ایستا | ثبات دست و بازو | تجسم | مهارت انگشتان | تقسیم توجه | انعطاف‌پذیری بستار | سرعت بستار | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | دقت کنترل | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان عملیات فرودگاهی | بازرسان ساختمان و سازه | مدیران مدیریت بحران و پدافند غیرعامل | بازرسان و کارشناسان بررسی علل حریق و حوادث | مهندسان ایمنی و حفاظت در برابر حریق | آتش‌نشانان | سرپرستان رده‌اول مشاغل ساختمانی و استخراج معدن | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی (به‌جز مراکز شرط‌بندی) | سرپرستان رده‌اول بخش کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول مهمانداران و مهمانداران خدمات مسافری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول نگهبانان و ماموران حراست | بازرسان و کارشناسان پیشگیری از حریق در جنگل‌ها و مراتع | مهندسان ایمنی و بهداشت حرفه‌ای (به‌جز مهندسان ایمنی معدن) | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های ایمنی و بهداشت حرفه‌ای | ماموران گشت پلیس و کلانتری | مهندسان موتورخانه کشتی و شناورها</t>
+          <t>کارشناسان عملیات فرودگاهی | بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت بحران و پدافند غیرعامل | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | آتش‌نشانان | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | ماموران گشت پلیس و کلانتری | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
